--- a/apps/template_docs/Citieslist.xlsx
+++ b/apps/template_docs/Citieslist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EGASP_PRO_06262025\EGASP_DATA\apps\template_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3271618A-6CE5-4B8A-B096-EFD0A16202D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F08AE-DCA0-41C2-B6EA-C2284B248D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BBC4C03-7E48-48E7-BAD6-2C29F0E83F49}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1662</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1663</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3324" uniqueCount="1524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="1525">
   <si>
     <t>City</t>
   </si>
@@ -4617,6 +4617,9 @@
   </si>
   <si>
     <t>Quezon City*</t>
+  </si>
+  <si>
+    <t>España</t>
   </si>
 </sst>
 </file>
@@ -4693,14 +4696,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4757,10 +4763,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3BE6FCF-2F5B-4A51-A0F3-10CE4CF7F59F}" name="Table_Table_25" displayName="Table_Table_25" ref="A1:B1662" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:B1662" xr:uid="{D3BE6FCF-2F5B-4A51-A0F3-10CE4CF7F59F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B1662">
-    <sortCondition ref="B1:B1662"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3BE6FCF-2F5B-4A51-A0F3-10CE4CF7F59F}" name="Table_Table_25" displayName="Table_Table_25" ref="A1:B1663" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:B1663" xr:uid="{D3BE6FCF-2F5B-4A51-A0F3-10CE4CF7F59F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B1663">
+    <sortCondition ref="B1:B1663"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{9A8DB001-22E9-4100-8F28-F516111C9F71}" uniqueName="1" name="City" queryTableFieldId="1" dataDxfId="2"/>
@@ -5067,7 +5073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A382C7B7-431D-474D-88E7-11B3AB6B22C6}">
-  <dimension ref="A1:B1662"/>
+  <dimension ref="A1:B1663"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -5299,7 +5305,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
@@ -7827,7 +7833,7 @@
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="4" t="s">
+      <c r="A345" t="s">
         <v>346</v>
       </c>
       <c r="B345" t="s">
@@ -8379,7 +8385,7 @@
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A414" s="4" t="s">
+      <c r="A414" t="s">
         <v>412</v>
       </c>
       <c r="B414" t="s">
@@ -8387,7 +8393,7 @@
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A415" s="4" t="s">
+      <c r="A415" t="s">
         <v>413</v>
       </c>
       <c r="B415" t="s">
@@ -10147,7 +10153,7 @@
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A635" s="4" t="s">
+      <c r="A635" t="s">
         <v>619</v>
       </c>
       <c r="B635" t="s">
@@ -10419,7 +10425,7 @@
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A669" s="4" t="s">
+      <c r="A669" t="s">
         <v>645</v>
       </c>
       <c r="B669" t="s">
@@ -10771,7 +10777,7 @@
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A713" s="4" t="s">
+      <c r="A713" t="s">
         <v>687</v>
       </c>
       <c r="B713" t="s">
@@ -12035,7 +12041,7 @@
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A871" s="4" t="s">
+      <c r="A871" t="s">
         <v>827</v>
       </c>
       <c r="B871" t="s">
@@ -12379,7 +12385,7 @@
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A914" s="4" t="s">
+      <c r="A914" t="s">
         <v>864</v>
       </c>
       <c r="B914" t="s">
@@ -12827,16 +12833,16 @@
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A970" t="s">
-        <v>904</v>
-      </c>
-      <c r="B970" t="s">
-        <v>905</v>
+      <c r="A970" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B970" s="5" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>30</v>
+        <v>904</v>
       </c>
       <c r="B971" t="s">
         <v>905</v>
@@ -12844,7 +12850,7 @@
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>906</v>
+        <v>30</v>
       </c>
       <c r="B972" t="s">
         <v>905</v>
@@ -12852,7 +12858,7 @@
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B973" t="s">
         <v>905</v>
@@ -12860,7 +12866,7 @@
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>534</v>
+        <v>907</v>
       </c>
       <c r="B974" t="s">
         <v>905</v>
@@ -12868,7 +12874,7 @@
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>908</v>
+        <v>534</v>
       </c>
       <c r="B975" t="s">
         <v>905</v>
@@ -12876,15 +12882,15 @@
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B976" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B977" t="s">
         <v>910</v>
@@ -12892,7 +12898,7 @@
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B978" t="s">
         <v>910</v>
@@ -12900,7 +12906,7 @@
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>222</v>
+        <v>912</v>
       </c>
       <c r="B979" t="s">
         <v>910</v>
@@ -12908,7 +12914,7 @@
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>913</v>
+        <v>222</v>
       </c>
       <c r="B980" t="s">
         <v>910</v>
@@ -12916,7 +12922,7 @@
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B981" t="s">
         <v>910</v>
@@ -12924,7 +12930,7 @@
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>317</v>
+        <v>914</v>
       </c>
       <c r="B982" t="s">
         <v>910</v>
@@ -12932,7 +12938,7 @@
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>915</v>
+        <v>317</v>
       </c>
       <c r="B983" t="s">
         <v>910</v>
@@ -12940,7 +12946,7 @@
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>46</v>
+        <v>915</v>
       </c>
       <c r="B984" t="s">
         <v>910</v>
@@ -12948,7 +12954,7 @@
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>916</v>
+        <v>46</v>
       </c>
       <c r="B985" t="s">
         <v>910</v>
@@ -12956,7 +12962,7 @@
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B986" t="s">
         <v>910</v>
@@ -12964,7 +12970,7 @@
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B987" t="s">
         <v>910</v>
@@ -12972,7 +12978,7 @@
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B988" t="s">
         <v>910</v>
@@ -12980,7 +12986,7 @@
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B989" t="s">
         <v>910</v>
@@ -12988,7 +12994,7 @@
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B990" t="s">
         <v>910</v>
@@ -12996,7 +13002,7 @@
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B991" t="s">
         <v>910</v>
@@ -13004,7 +13010,7 @@
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B992" t="s">
         <v>910</v>
@@ -13012,7 +13018,7 @@
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>278</v>
+        <v>923</v>
       </c>
       <c r="B993" t="s">
         <v>910</v>
@@ -13020,7 +13026,7 @@
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>924</v>
+        <v>278</v>
       </c>
       <c r="B994" t="s">
         <v>910</v>
@@ -13028,7 +13034,7 @@
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>183</v>
+        <v>924</v>
       </c>
       <c r="B995" t="s">
         <v>910</v>
@@ -13036,7 +13042,7 @@
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>925</v>
+        <v>183</v>
       </c>
       <c r="B996" t="s">
         <v>910</v>
@@ -13044,15 +13050,15 @@
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B997" t="s">
-        <v>927</v>
+        <v>910</v>
       </c>
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B998" t="s">
         <v>927</v>
@@ -13060,7 +13066,7 @@
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B999" t="s">
         <v>927</v>
@@ -13068,7 +13074,7 @@
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B1000" t="s">
         <v>927</v>
@@ -13076,7 +13082,7 @@
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B1001" t="s">
         <v>927</v>
@@ -13084,7 +13090,7 @@
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B1002" t="s">
         <v>927</v>
@@ -13092,7 +13098,7 @@
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B1003" t="s">
         <v>927</v>
@@ -13100,7 +13106,7 @@
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B1004" t="s">
         <v>927</v>
@@ -13108,7 +13114,7 @@
     </row>
     <row r="1005" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B1005" t="s">
         <v>927</v>
@@ -13116,7 +13122,7 @@
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B1006" t="s">
         <v>927</v>
@@ -13124,7 +13130,7 @@
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B1007" t="s">
         <v>927</v>
@@ -13132,7 +13138,7 @@
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B1008" t="s">
         <v>927</v>
@@ -13140,7 +13146,7 @@
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B1009" t="s">
         <v>927</v>
@@ -13148,7 +13154,7 @@
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>1523</v>
+        <v>939</v>
       </c>
       <c r="B1010" t="s">
         <v>927</v>
@@ -13156,7 +13162,7 @@
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>24</v>
+        <v>1523</v>
       </c>
       <c r="B1011" t="s">
         <v>927</v>
@@ -13164,7 +13170,7 @@
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>940</v>
+        <v>24</v>
       </c>
       <c r="B1012" t="s">
         <v>927</v>
@@ -13172,7 +13178,7 @@
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B1013" t="s">
         <v>927</v>
@@ -13180,15 +13186,15 @@
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B1014" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B1015" t="s">
         <v>943</v>
@@ -13196,7 +13202,7 @@
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B1016" t="s">
         <v>943</v>
@@ -13204,7 +13210,7 @@
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B1017" t="s">
         <v>943</v>
@@ -13212,7 +13218,7 @@
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>1506</v>
+        <v>946</v>
       </c>
       <c r="B1018" t="s">
         <v>943</v>
@@ -13220,7 +13226,7 @@
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>660</v>
+        <v>1506</v>
       </c>
       <c r="B1019" t="s">
         <v>943</v>
@@ -13228,7 +13234,7 @@
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>947</v>
+        <v>660</v>
       </c>
       <c r="B1020" t="s">
         <v>943</v>
@@ -13236,7 +13242,7 @@
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B1021" t="s">
         <v>943</v>
@@ -13244,7 +13250,7 @@
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B1022" t="s">
         <v>943</v>
@@ -13252,7 +13258,7 @@
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B1023" t="s">
         <v>943</v>
@@ -13260,7 +13266,7 @@
     </row>
     <row r="1024" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B1024" t="s">
         <v>943</v>
@@ -13268,7 +13274,7 @@
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B1025" t="s">
         <v>943</v>
@@ -13276,7 +13282,7 @@
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>300</v>
+        <v>952</v>
       </c>
       <c r="B1026" t="s">
         <v>943</v>
@@ -13284,7 +13290,7 @@
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>953</v>
+        <v>300</v>
       </c>
       <c r="B1027" t="s">
         <v>943</v>
@@ -13292,7 +13298,7 @@
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B1028" t="s">
         <v>943</v>
@@ -13300,7 +13306,7 @@
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B1029" t="s">
         <v>943</v>
@@ -13308,7 +13314,7 @@
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>481</v>
+        <v>955</v>
       </c>
       <c r="B1030" t="s">
         <v>943</v>
@@ -13316,15 +13322,15 @@
     </row>
     <row r="1031" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>956</v>
+        <v>481</v>
       </c>
       <c r="B1031" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B1032" t="s">
         <v>957</v>
@@ -13332,7 +13338,7 @@
     </row>
     <row r="1033" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B1033" t="s">
         <v>957</v>
@@ -13340,7 +13346,7 @@
     </row>
     <row r="1034" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B1034" t="s">
         <v>957</v>
@@ -13348,7 +13354,7 @@
     </row>
     <row r="1035" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B1035" t="s">
         <v>957</v>
@@ -13356,7 +13362,7 @@
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>317</v>
+        <v>961</v>
       </c>
       <c r="B1036" t="s">
         <v>957</v>
@@ -13364,7 +13370,7 @@
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>962</v>
+        <v>317</v>
       </c>
       <c r="B1037" t="s">
         <v>957</v>
@@ -13372,7 +13378,7 @@
     </row>
     <row r="1038" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B1038" t="s">
         <v>957</v>
@@ -13380,7 +13386,7 @@
     </row>
     <row r="1039" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B1039" t="s">
         <v>957</v>
@@ -13388,7 +13394,7 @@
     </row>
     <row r="1040" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B1040" t="s">
         <v>957</v>
@@ -13396,7 +13402,7 @@
     </row>
     <row r="1041" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B1041" t="s">
         <v>957</v>
@@ -13404,7 +13410,7 @@
     </row>
     <row r="1042" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B1042" t="s">
         <v>957</v>
@@ -13412,7 +13418,7 @@
     </row>
     <row r="1043" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B1043" t="s">
         <v>957</v>
@@ -13420,7 +13426,7 @@
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B1044" t="s">
         <v>957</v>
@@ -13428,7 +13434,7 @@
     </row>
     <row r="1045" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>102</v>
+        <v>969</v>
       </c>
       <c r="B1045" t="s">
         <v>957</v>
@@ -13436,7 +13442,7 @@
     </row>
     <row r="1046" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>970</v>
+        <v>102</v>
       </c>
       <c r="B1046" t="s">
         <v>957</v>
@@ -13444,7 +13450,7 @@
     </row>
     <row r="1047" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>530</v>
+        <v>970</v>
       </c>
       <c r="B1047" t="s">
         <v>957</v>
@@ -13452,7 +13458,7 @@
     </row>
     <row r="1048" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>971</v>
+        <v>530</v>
       </c>
       <c r="B1048" t="s">
         <v>957</v>
@@ -13460,7 +13466,7 @@
     </row>
     <row r="1049" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B1049" t="s">
         <v>957</v>
@@ -13468,7 +13474,7 @@
     </row>
     <row r="1050" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B1050" t="s">
         <v>957</v>
@@ -13476,7 +13482,7 @@
     </row>
     <row r="1051" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B1051" t="s">
         <v>957</v>
@@ -13484,7 +13490,7 @@
     </row>
     <row r="1052" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B1052" t="s">
         <v>957</v>
@@ -13492,7 +13498,7 @@
     </row>
     <row r="1053" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B1053" t="s">
         <v>957</v>
@@ -13500,7 +13506,7 @@
     </row>
     <row r="1054" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>785</v>
+        <v>976</v>
       </c>
       <c r="B1054" t="s">
         <v>957</v>
@@ -13508,15 +13514,15 @@
     </row>
     <row r="1055" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>977</v>
+        <v>785</v>
       </c>
       <c r="B1055" t="s">
         <v>957</v>
       </c>
     </row>
     <row r="1056" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1056" s="4" t="s">
-        <v>978</v>
+      <c r="A1056" t="s">
+        <v>977</v>
       </c>
       <c r="B1056" t="s">
         <v>957</v>
@@ -13524,15 +13530,15 @@
     </row>
     <row r="1057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B1057" t="s">
-        <v>980</v>
+        <v>957</v>
       </c>
     </row>
     <row r="1058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B1058" t="s">
         <v>980</v>
@@ -13540,7 +13546,7 @@
     </row>
     <row r="1059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B1059" t="s">
         <v>980</v>
@@ -13548,7 +13554,7 @@
     </row>
     <row r="1060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>1500</v>
+        <v>982</v>
       </c>
       <c r="B1060" t="s">
         <v>980</v>
@@ -13556,7 +13562,7 @@
     </row>
     <row r="1061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>984</v>
+        <v>1500</v>
       </c>
       <c r="B1061" t="s">
         <v>980</v>
@@ -13564,7 +13570,7 @@
     </row>
     <row r="1062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1062" t="s">
         <v>980</v>
@@ -13572,7 +13578,7 @@
     </row>
     <row r="1063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1063" t="s">
         <v>980</v>
@@ -13580,7 +13586,7 @@
     </row>
     <row r="1064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B1064" t="s">
         <v>980</v>
@@ -13588,7 +13594,7 @@
     </row>
     <row r="1065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1065" t="s">
         <v>980</v>
@@ -13596,7 +13602,7 @@
     </row>
     <row r="1066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1066" t="s">
         <v>980</v>
@@ -13604,15 +13610,15 @@
     </row>
     <row r="1067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1067" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B1068" t="s">
         <v>991</v>
@@ -13620,7 +13626,7 @@
     </row>
     <row r="1069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1069" t="s">
         <v>991</v>
@@ -13628,7 +13634,7 @@
     </row>
     <row r="1070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1070" t="s">
         <v>991</v>
@@ -13636,7 +13642,7 @@
     </row>
     <row r="1071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>1502</v>
+        <v>994</v>
       </c>
       <c r="B1071" t="s">
         <v>991</v>
@@ -13644,7 +13650,7 @@
     </row>
     <row r="1072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>996</v>
+        <v>1502</v>
       </c>
       <c r="B1072" t="s">
         <v>991</v>
@@ -13652,7 +13658,7 @@
     </row>
     <row r="1073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>1505</v>
+        <v>996</v>
       </c>
       <c r="B1073" t="s">
         <v>991</v>
@@ -13660,7 +13666,7 @@
     </row>
     <row r="1074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
-        <v>997</v>
+        <v>1505</v>
       </c>
       <c r="B1074" t="s">
         <v>991</v>
@@ -13668,7 +13674,7 @@
     </row>
     <row r="1075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1075" t="s">
         <v>991</v>
@@ -13676,7 +13682,7 @@
     </row>
     <row r="1076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1076" t="s">
         <v>991</v>
@@ -13684,7 +13690,7 @@
     </row>
     <row r="1077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1077" t="s">
         <v>991</v>
@@ -13692,7 +13698,7 @@
     </row>
     <row r="1078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B1078" t="s">
         <v>991</v>
@@ -13700,7 +13706,7 @@
     </row>
     <row r="1079" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B1079" t="s">
         <v>991</v>
@@ -13708,7 +13714,7 @@
     </row>
     <row r="1080" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B1080" t="s">
         <v>991</v>
@@ -13716,7 +13722,7 @@
     </row>
     <row r="1081" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>688</v>
+        <v>1003</v>
       </c>
       <c r="B1081" t="s">
         <v>991</v>
@@ -13724,7 +13730,7 @@
     </row>
     <row r="1082" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>1004</v>
+        <v>688</v>
       </c>
       <c r="B1082" t="s">
         <v>991</v>
@@ -13732,7 +13738,7 @@
     </row>
     <row r="1083" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B1083" t="s">
         <v>991</v>
@@ -13740,7 +13746,7 @@
     </row>
     <row r="1084" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B1084" t="s">
         <v>991</v>
@@ -13748,7 +13754,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B1085" t="s">
         <v>991</v>
@@ -13756,7 +13762,7 @@
     </row>
     <row r="1086" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B1086" t="s">
         <v>991</v>
@@ -13764,7 +13770,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B1087" t="s">
         <v>991</v>
@@ -13772,7 +13778,7 @@
     </row>
     <row r="1088" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>399</v>
+        <v>1009</v>
       </c>
       <c r="B1088" t="s">
         <v>991</v>
@@ -13780,7 +13786,7 @@
     </row>
     <row r="1089" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>1010</v>
+        <v>399</v>
       </c>
       <c r="B1089" t="s">
         <v>991</v>
@@ -13788,7 +13794,7 @@
     </row>
     <row r="1090" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>387</v>
+        <v>1010</v>
       </c>
       <c r="B1090" t="s">
         <v>991</v>
@@ -13796,7 +13802,7 @@
     </row>
     <row r="1091" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>1011</v>
+        <v>387</v>
       </c>
       <c r="B1091" t="s">
         <v>991</v>
@@ -13804,7 +13810,7 @@
     </row>
     <row r="1092" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>681</v>
+        <v>1011</v>
       </c>
       <c r="B1092" t="s">
         <v>991</v>
@@ -13812,7 +13818,7 @@
     </row>
     <row r="1093" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>1012</v>
+        <v>681</v>
       </c>
       <c r="B1093" t="s">
         <v>991</v>
@@ -13820,7 +13826,7 @@
     </row>
     <row r="1094" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B1094" t="s">
         <v>991</v>
@@ -13828,7 +13834,7 @@
     </row>
     <row r="1095" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>187</v>
+        <v>1013</v>
       </c>
       <c r="B1095" t="s">
         <v>991</v>
@@ -13836,7 +13842,7 @@
     </row>
     <row r="1096" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>1014</v>
+        <v>187</v>
       </c>
       <c r="B1096" t="s">
         <v>991</v>
@@ -13844,7 +13850,7 @@
     </row>
     <row r="1097" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B1097" t="s">
         <v>991</v>
@@ -13852,7 +13858,7 @@
     </row>
     <row r="1098" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B1098" t="s">
         <v>991</v>
@@ -13860,15 +13866,15 @@
     </row>
     <row r="1099" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1099" t="s">
-        <v>1018</v>
+        <v>991</v>
       </c>
     </row>
     <row r="1100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B1100" t="s">
         <v>1018</v>
@@ -13876,7 +13882,7 @@
     </row>
     <row r="1101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B1101" t="s">
         <v>1018</v>
@@ -13884,7 +13890,7 @@
     </row>
     <row r="1102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1102" t="s">
         <v>1018</v>
@@ -13892,7 +13898,7 @@
     </row>
     <row r="1103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B1103" t="s">
         <v>1018</v>
@@ -13900,7 +13906,7 @@
     </row>
     <row r="1104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B1104" t="s">
         <v>1018</v>
@@ -13908,7 +13914,7 @@
     </row>
     <row r="1105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B1105" t="s">
         <v>1018</v>
@@ -13916,7 +13922,7 @@
     </row>
     <row r="1106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B1106" t="s">
         <v>1018</v>
@@ -13924,7 +13930,7 @@
     </row>
     <row r="1107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B1107" t="s">
         <v>1018</v>
@@ -13932,7 +13938,7 @@
     </row>
     <row r="1108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B1108" t="s">
         <v>1018</v>
@@ -13940,7 +13946,7 @@
     </row>
     <row r="1109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B1109" t="s">
         <v>1018</v>
@@ -13948,7 +13954,7 @@
     </row>
     <row r="1110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B1110" t="s">
         <v>1018</v>
@@ -13956,7 +13962,7 @@
     </row>
     <row r="1111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B1111" t="s">
         <v>1018</v>
@@ -13964,7 +13970,7 @@
     </row>
     <row r="1112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B1112" t="s">
         <v>1018</v>
@@ -13972,7 +13978,7 @@
     </row>
     <row r="1113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B1113" t="s">
         <v>1018</v>
@@ -13980,7 +13986,7 @@
     </row>
     <row r="1114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>324</v>
+        <v>1032</v>
       </c>
       <c r="B1114" t="s">
         <v>1018</v>
@@ -13988,7 +13994,7 @@
     </row>
     <row r="1115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="B1115" t="s">
         <v>1018</v>
@@ -13996,7 +14002,7 @@
     </row>
     <row r="1116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>637</v>
+        <v>181</v>
       </c>
       <c r="B1116" t="s">
         <v>1018</v>
@@ -14004,7 +14010,7 @@
     </row>
     <row r="1117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>1033</v>
+        <v>637</v>
       </c>
       <c r="B1117" t="s">
         <v>1018</v>
@@ -14012,7 +14018,7 @@
     </row>
     <row r="1118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B1118" t="s">
         <v>1018</v>
@@ -14020,7 +14026,7 @@
     </row>
     <row r="1119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B1119" t="s">
         <v>1018</v>
@@ -14028,7 +14034,7 @@
     </row>
     <row r="1120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B1120" t="s">
         <v>1018</v>
@@ -14036,7 +14042,7 @@
     </row>
     <row r="1121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>258</v>
+        <v>1036</v>
       </c>
       <c r="B1121" t="s">
         <v>1018</v>
@@ -14044,15 +14050,15 @@
     </row>
     <row r="1122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>1037</v>
+        <v>258</v>
       </c>
       <c r="B1122" t="s">
         <v>1018</v>
       </c>
     </row>
     <row r="1123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1123" s="4" t="s">
-        <v>1038</v>
+      <c r="A1123" t="s">
+        <v>1037</v>
       </c>
       <c r="B1123" t="s">
         <v>1018</v>
@@ -14060,15 +14066,15 @@
     </row>
     <row r="1124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B1124" t="s">
-        <v>1040</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="1125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B1125" t="s">
         <v>1040</v>
@@ -14076,7 +14082,7 @@
     </row>
     <row r="1126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B1126" t="s">
         <v>1040</v>
@@ -14084,7 +14090,7 @@
     </row>
     <row r="1127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B1127" t="s">
         <v>1040</v>
@@ -14092,7 +14098,7 @@
     </row>
     <row r="1128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B1128" t="s">
         <v>1040</v>
@@ -14100,7 +14106,7 @@
     </row>
     <row r="1129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B1129" t="s">
         <v>1040</v>
@@ -14108,7 +14114,7 @@
     </row>
     <row r="1130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B1130" t="s">
         <v>1040</v>
@@ -14116,7 +14122,7 @@
     </row>
     <row r="1131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B1131" t="s">
         <v>1040</v>
@@ -14124,7 +14130,7 @@
     </row>
     <row r="1132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B1132" t="s">
         <v>1040</v>
@@ -14132,7 +14138,7 @@
     </row>
     <row r="1133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B1133" t="s">
         <v>1040</v>
@@ -14140,7 +14146,7 @@
     </row>
     <row r="1134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B1134" t="s">
         <v>1040</v>
@@ -14148,7 +14154,7 @@
     </row>
     <row r="1135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B1135" t="s">
         <v>1040</v>
@@ -14156,7 +14162,7 @@
     </row>
     <row r="1136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B1136" t="s">
         <v>1040</v>
@@ -14164,7 +14170,7 @@
     </row>
     <row r="1137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B1137" t="s">
         <v>1040</v>
@@ -14172,7 +14178,7 @@
     </row>
     <row r="1138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1138" t="s">
         <v>1040</v>
@@ -14180,7 +14186,7 @@
     </row>
     <row r="1139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B1139" t="s">
         <v>1040</v>
@@ -14188,7 +14194,7 @@
     </row>
     <row r="1140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>49</v>
+        <v>1055</v>
       </c>
       <c r="B1140" t="s">
         <v>1040</v>
@@ -14196,7 +14202,7 @@
     </row>
     <row r="1141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>1056</v>
+        <v>49</v>
       </c>
       <c r="B1141" t="s">
         <v>1040</v>
@@ -14204,7 +14210,7 @@
     </row>
     <row r="1142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>23</v>
+        <v>1056</v>
       </c>
       <c r="B1142" t="s">
         <v>1040</v>
@@ -14212,7 +14218,7 @@
     </row>
     <row r="1143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="B1143" t="s">
         <v>1040</v>
@@ -14220,7 +14226,7 @@
     </row>
     <row r="1144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>1057</v>
+        <v>181</v>
       </c>
       <c r="B1144" t="s">
         <v>1040</v>
@@ -14228,7 +14234,7 @@
     </row>
     <row r="1145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
-        <v>344</v>
+        <v>1057</v>
       </c>
       <c r="B1145" t="s">
         <v>1040</v>
@@ -14236,7 +14242,7 @@
     </row>
     <row r="1146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>1058</v>
+        <v>344</v>
       </c>
       <c r="B1146" t="s">
         <v>1040</v>
@@ -14244,7 +14250,7 @@
     </row>
     <row r="1147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>764</v>
+        <v>1058</v>
       </c>
       <c r="B1147" t="s">
         <v>1040</v>
@@ -14252,15 +14258,15 @@
     </row>
     <row r="1148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>1059</v>
+        <v>764</v>
       </c>
       <c r="B1148" t="s">
-        <v>1060</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="1149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B1149" t="s">
         <v>1060</v>
@@ -14268,7 +14274,7 @@
     </row>
     <row r="1150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B1150" t="s">
         <v>1060</v>
@@ -14276,7 +14282,7 @@
     </row>
     <row r="1151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B1151" t="s">
         <v>1060</v>
@@ -14284,7 +14290,7 @@
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B1152" t="s">
         <v>1060</v>
@@ -14292,7 +14298,7 @@
     </row>
     <row r="1153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B1153" t="s">
         <v>1060</v>
@@ -14300,7 +14306,7 @@
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B1154" t="s">
         <v>1060</v>
@@ -14308,7 +14314,7 @@
     </row>
     <row r="1155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B1155" t="s">
         <v>1060</v>
@@ -14316,7 +14322,7 @@
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B1156" t="s">
         <v>1060</v>
@@ -14324,7 +14330,7 @@
     </row>
     <row r="1157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B1157" t="s">
         <v>1060</v>
@@ -14332,7 +14338,7 @@
     </row>
     <row r="1158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B1158" t="s">
         <v>1060</v>
@@ -14340,7 +14346,7 @@
     </row>
     <row r="1159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B1159" t="s">
         <v>1060</v>
@@ -14348,7 +14354,7 @@
     </row>
     <row r="1160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B1160" t="s">
         <v>1060</v>
@@ -14356,7 +14362,7 @@
     </row>
     <row r="1161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B1161" t="s">
         <v>1060</v>
@@ -14364,7 +14370,7 @@
     </row>
     <row r="1162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B1162" t="s">
         <v>1060</v>
@@ -14372,7 +14378,7 @@
     </row>
     <row r="1163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B1163" t="s">
         <v>1060</v>
@@ -14380,7 +14386,7 @@
     </row>
     <row r="1164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B1164" t="s">
         <v>1060</v>
@@ -14388,7 +14394,7 @@
     </row>
     <row r="1165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B1165" t="s">
         <v>1060</v>
@@ -14396,7 +14402,7 @@
     </row>
     <row r="1166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B1166" t="s">
         <v>1060</v>
@@ -14404,7 +14410,7 @@
     </row>
     <row r="1167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B1167" t="s">
         <v>1060</v>
@@ -14412,7 +14418,7 @@
     </row>
     <row r="1168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B1168" t="s">
         <v>1060</v>
@@ -14420,7 +14426,7 @@
     </row>
     <row r="1169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>277</v>
+        <v>1080</v>
       </c>
       <c r="B1169" t="s">
         <v>1060</v>
@@ -14428,7 +14434,7 @@
     </row>
     <row r="1170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="B1170" t="s">
         <v>1060</v>
@@ -14436,7 +14442,7 @@
     </row>
     <row r="1171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>1056</v>
+        <v>327</v>
       </c>
       <c r="B1171" t="s">
         <v>1060</v>
@@ -14444,7 +14450,7 @@
     </row>
     <row r="1172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>23</v>
+        <v>1056</v>
       </c>
       <c r="B1172" t="s">
         <v>1060</v>
@@ -14452,7 +14458,7 @@
     </row>
     <row r="1173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="B1173" t="s">
         <v>1060</v>
@@ -14460,7 +14466,7 @@
     </row>
     <row r="1174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>1081</v>
+        <v>181</v>
       </c>
       <c r="B1174" t="s">
         <v>1060</v>
@@ -14468,7 +14474,7 @@
     </row>
     <row r="1175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
-        <v>762</v>
+        <v>1081</v>
       </c>
       <c r="B1175" t="s">
         <v>1060</v>
@@ -14476,7 +14482,7 @@
     </row>
     <row r="1176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>90</v>
+        <v>762</v>
       </c>
       <c r="B1176" t="s">
         <v>1060</v>
@@ -14484,7 +14490,7 @@
     </row>
     <row r="1177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
-        <v>1082</v>
+        <v>90</v>
       </c>
       <c r="B1177" t="s">
         <v>1060</v>
@@ -14492,15 +14498,15 @@
     </row>
     <row r="1178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B1178" t="s">
         <v>1060</v>
       </c>
     </row>
     <row r="1179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1179" s="4" t="s">
-        <v>1084</v>
+      <c r="A1179" t="s">
+        <v>1083</v>
       </c>
       <c r="B1179" t="s">
         <v>1060</v>
@@ -14508,15 +14514,15 @@
     </row>
     <row r="1180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B1180" t="s">
-        <v>1086</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B1181" t="s">
         <v>1086</v>
@@ -14524,7 +14530,7 @@
     </row>
     <row r="1182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B1182" t="s">
         <v>1086</v>
@@ -14532,7 +14538,7 @@
     </row>
     <row r="1183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B1183" t="s">
         <v>1086</v>
@@ -14540,7 +14546,7 @@
     </row>
     <row r="1184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B1184" t="s">
         <v>1086</v>
@@ -14548,7 +14554,7 @@
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B1185" t="s">
         <v>1086</v>
@@ -14556,7 +14562,7 @@
     </row>
     <row r="1186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B1186" t="s">
         <v>1086</v>
@@ -14564,7 +14570,7 @@
     </row>
     <row r="1187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B1187" t="s">
         <v>1086</v>
@@ -14572,7 +14578,7 @@
     </row>
     <row r="1188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B1188" t="s">
         <v>1086</v>
@@ -14580,7 +14586,7 @@
     </row>
     <row r="1189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B1189" t="s">
         <v>1086</v>
@@ -14588,7 +14594,7 @@
     </row>
     <row r="1190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B1190" t="s">
         <v>1086</v>
@@ -14596,7 +14602,7 @@
     </row>
     <row r="1191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
-        <v>277</v>
+        <v>1096</v>
       </c>
       <c r="B1191" t="s">
         <v>1086</v>
@@ -14604,7 +14610,7 @@
     </row>
     <row r="1192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>474</v>
+        <v>277</v>
       </c>
       <c r="B1192" t="s">
         <v>1086</v>
@@ -14612,15 +14618,15 @@
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
-        <v>1097</v>
+        <v>474</v>
       </c>
       <c r="B1193" t="s">
         <v>1086</v>
       </c>
     </row>
     <row r="1194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1194" s="4" t="s">
-        <v>1098</v>
+      <c r="A1194" t="s">
+        <v>1097</v>
       </c>
       <c r="B1194" t="s">
         <v>1086</v>
@@ -14628,15 +14634,15 @@
     </row>
     <row r="1195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B1195" t="s">
-        <v>1100</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B1196" t="s">
         <v>1100</v>
@@ -14644,7 +14650,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B1197" t="s">
         <v>1100</v>
@@ -14652,7 +14658,7 @@
     </row>
     <row r="1198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B1198" t="s">
         <v>1100</v>
@@ -14660,7 +14666,7 @@
     </row>
     <row r="1199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>530</v>
+        <v>1103</v>
       </c>
       <c r="B1199" t="s">
         <v>1100</v>
@@ -14668,7 +14674,7 @@
     </row>
     <row r="1200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>1104</v>
+        <v>530</v>
       </c>
       <c r="B1200" t="s">
         <v>1100</v>
@@ -14676,7 +14682,7 @@
     </row>
     <row r="1201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B1201" t="s">
         <v>1100</v>
@@ -14684,7 +14690,7 @@
     </row>
     <row r="1202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
-        <v>327</v>
+        <v>1105</v>
       </c>
       <c r="B1202" t="s">
         <v>1100</v>
@@ -14692,7 +14698,7 @@
     </row>
     <row r="1203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>1106</v>
+        <v>327</v>
       </c>
       <c r="B1203" t="s">
         <v>1100</v>
@@ -14700,7 +14706,7 @@
     </row>
     <row r="1204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B1204" t="s">
         <v>1100</v>
@@ -14708,7 +14714,7 @@
     </row>
     <row r="1205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
-        <v>534</v>
+        <v>1107</v>
       </c>
       <c r="B1205" t="s">
         <v>1100</v>
@@ -14716,15 +14722,15 @@
     </row>
     <row r="1206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
-        <v>1108</v>
+        <v>534</v>
       </c>
       <c r="B1206" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B1207" t="s">
         <v>1109</v>
@@ -14732,7 +14738,7 @@
     </row>
     <row r="1208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B1208" t="s">
         <v>1109</v>
@@ -14740,7 +14746,7 @@
     </row>
     <row r="1209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B1209" t="s">
         <v>1109</v>
@@ -14748,7 +14754,7 @@
     </row>
     <row r="1210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B1210" t="s">
         <v>1109</v>
@@ -14756,7 +14762,7 @@
     </row>
     <row r="1211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B1211" t="s">
         <v>1109</v>
@@ -14764,7 +14770,7 @@
     </row>
     <row r="1212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B1212" t="s">
         <v>1109</v>
@@ -14772,7 +14778,7 @@
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B1213" t="s">
         <v>1109</v>
@@ -14780,7 +14786,7 @@
     </row>
     <row r="1214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B1214" t="s">
         <v>1109</v>
@@ -14788,7 +14794,7 @@
     </row>
     <row r="1215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B1215" t="s">
         <v>1109</v>
@@ -14796,7 +14802,7 @@
     </row>
     <row r="1216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B1216" t="s">
         <v>1109</v>
@@ -14804,7 +14810,7 @@
     </row>
     <row r="1217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>707</v>
+        <v>1119</v>
       </c>
       <c r="B1217" t="s">
         <v>1109</v>
@@ -14812,7 +14818,7 @@
     </row>
     <row r="1218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
-        <v>1120</v>
+        <v>707</v>
       </c>
       <c r="B1218" t="s">
         <v>1109</v>
@@ -14820,7 +14826,7 @@
     </row>
     <row r="1219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B1219" t="s">
         <v>1109</v>
@@ -14828,7 +14834,7 @@
     </row>
     <row r="1220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
-        <v>764</v>
+        <v>1121</v>
       </c>
       <c r="B1220" t="s">
         <v>1109</v>
@@ -14836,15 +14842,15 @@
     </row>
     <row r="1221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
-        <v>1122</v>
+        <v>764</v>
       </c>
       <c r="B1221" t="s">
-        <v>1123</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1222" t="s">
         <v>1123</v>
@@ -14852,7 +14858,7 @@
     </row>
     <row r="1223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1223" t="s">
         <v>1123</v>
@@ -14860,7 +14866,7 @@
     </row>
     <row r="1224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1224" t="s">
         <v>1123</v>
@@ -14868,7 +14874,7 @@
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1225" t="s">
         <v>1123</v>
@@ -14876,7 +14882,7 @@
     </row>
     <row r="1226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1226" t="s">
         <v>1123</v>
@@ -14884,7 +14890,7 @@
     </row>
     <row r="1227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1227" t="s">
         <v>1123</v>
@@ -14892,7 +14898,7 @@
     </row>
     <row r="1228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1228" t="s">
         <v>1123</v>
@@ -14900,7 +14906,7 @@
     </row>
     <row r="1229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1229" t="s">
         <v>1123</v>
@@ -14908,7 +14914,7 @@
     </row>
     <row r="1230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1230" t="s">
         <v>1123</v>
@@ -14916,7 +14922,7 @@
     </row>
     <row r="1231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1231" t="s">
         <v>1123</v>
@@ -14924,7 +14930,7 @@
     </row>
     <row r="1232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1232" t="s">
         <v>1123</v>
@@ -14932,7 +14938,7 @@
     </row>
     <row r="1233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1233" t="s">
         <v>1123</v>
@@ -14940,7 +14946,7 @@
     </row>
     <row r="1234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1234" t="s">
-        <v>747</v>
+        <v>1135</v>
       </c>
       <c r="B1234" t="s">
         <v>1123</v>
@@ -14948,7 +14954,7 @@
     </row>
     <row r="1235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>1136</v>
+        <v>747</v>
       </c>
       <c r="B1235" t="s">
         <v>1123</v>
@@ -14956,7 +14962,7 @@
     </row>
     <row r="1236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>530</v>
+        <v>1136</v>
       </c>
       <c r="B1236" t="s">
         <v>1123</v>
@@ -14964,7 +14970,7 @@
     </row>
     <row r="1237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1237" t="s">
-        <v>1137</v>
+        <v>530</v>
       </c>
       <c r="B1237" t="s">
         <v>1123</v>
@@ -14972,7 +14978,7 @@
     </row>
     <row r="1238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B1238" t="s">
         <v>1123</v>
@@ -14980,7 +14986,7 @@
     </row>
     <row r="1239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>277</v>
+        <v>1138</v>
       </c>
       <c r="B1239" t="s">
         <v>1123</v>
@@ -14988,7 +14994,7 @@
     </row>
     <row r="1240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="B1240" t="s">
         <v>1123</v>
@@ -14996,7 +15002,7 @@
     </row>
     <row r="1241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1241" t="s">
-        <v>707</v>
+        <v>327</v>
       </c>
       <c r="B1241" t="s">
         <v>1123</v>
@@ -15004,7 +15010,7 @@
     </row>
     <row r="1242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
-        <v>344</v>
+        <v>707</v>
       </c>
       <c r="B1242" t="s">
         <v>1123</v>
@@ -15012,7 +15018,7 @@
     </row>
     <row r="1243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
-        <v>1139</v>
+        <v>344</v>
       </c>
       <c r="B1243" t="s">
         <v>1123</v>
@@ -15020,7 +15026,7 @@
     </row>
     <row r="1244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B1244" t="s">
         <v>1123</v>
@@ -15028,15 +15034,15 @@
     </row>
     <row r="1245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1245" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B1245" t="s">
-        <v>1142</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B1246" t="s">
         <v>1142</v>
@@ -15044,7 +15050,7 @@
     </row>
     <row r="1247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B1247" t="s">
         <v>1142</v>
@@ -15052,7 +15058,7 @@
     </row>
     <row r="1248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B1248" t="s">
         <v>1142</v>
@@ -15060,7 +15066,7 @@
     </row>
     <row r="1249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B1249" t="s">
         <v>1142</v>
@@ -15068,7 +15074,7 @@
     </row>
     <row r="1250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1250" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B1250" t="s">
         <v>1142</v>
@@ -15076,7 +15082,7 @@
     </row>
     <row r="1251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B1251" t="s">
         <v>1142</v>
@@ -15084,7 +15090,7 @@
     </row>
     <row r="1252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B1252" t="s">
         <v>1142</v>
@@ -15092,7 +15098,7 @@
     </row>
     <row r="1253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B1253" t="s">
         <v>1142</v>
@@ -15100,7 +15106,7 @@
     </row>
     <row r="1254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1254" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B1254" t="s">
         <v>1142</v>
@@ -15108,7 +15114,7 @@
     </row>
     <row r="1255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B1255" t="s">
         <v>1142</v>
@@ -15116,7 +15122,7 @@
     </row>
     <row r="1256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B1256" t="s">
         <v>1142</v>
@@ -15124,7 +15130,7 @@
     </row>
     <row r="1257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B1257" t="s">
         <v>1142</v>
@@ -15132,7 +15138,7 @@
     </row>
     <row r="1258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1258" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B1258" t="s">
         <v>1142</v>
@@ -15140,7 +15146,7 @@
     </row>
     <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B1259" t="s">
         <v>1142</v>
@@ -15148,7 +15154,7 @@
     </row>
     <row r="1260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
-        <v>278</v>
+        <v>1156</v>
       </c>
       <c r="B1260" t="s">
         <v>1142</v>
@@ -15156,7 +15162,7 @@
     </row>
     <row r="1261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
-        <v>51</v>
+        <v>278</v>
       </c>
       <c r="B1261" t="s">
         <v>1142</v>
@@ -15164,7 +15170,7 @@
     </row>
     <row r="1262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
-        <v>1157</v>
+        <v>51</v>
       </c>
       <c r="B1262" t="s">
         <v>1142</v>
@@ -15172,7 +15178,7 @@
     </row>
     <row r="1263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>329</v>
+        <v>1157</v>
       </c>
       <c r="B1263" t="s">
         <v>1142</v>
@@ -15180,7 +15186,7 @@
     </row>
     <row r="1264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>1158</v>
+        <v>329</v>
       </c>
       <c r="B1264" t="s">
         <v>1142</v>
@@ -15188,7 +15194,7 @@
     </row>
     <row r="1265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1265" t="s">
-        <v>185</v>
+        <v>1158</v>
       </c>
       <c r="B1265" t="s">
         <v>1142</v>
@@ -15196,7 +15202,7 @@
     </row>
     <row r="1266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1266" t="s">
-        <v>1159</v>
+        <v>185</v>
       </c>
       <c r="B1266" t="s">
         <v>1142</v>
@@ -15204,15 +15210,15 @@
     </row>
     <row r="1267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B1267" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B1268" t="s">
         <v>1161</v>
@@ -15220,7 +15226,7 @@
     </row>
     <row r="1269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>738</v>
+        <v>1162</v>
       </c>
       <c r="B1269" t="s">
         <v>1161</v>
@@ -15228,7 +15234,7 @@
     </row>
     <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>308</v>
+        <v>738</v>
       </c>
       <c r="B1270" t="s">
         <v>1161</v>
@@ -15236,7 +15242,7 @@
     </row>
     <row r="1271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="B1271" t="s">
         <v>1161</v>
@@ -15244,7 +15250,7 @@
     </row>
     <row r="1272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>1163</v>
+        <v>218</v>
       </c>
       <c r="B1272" t="s">
         <v>1161</v>
@@ -15252,7 +15258,7 @@
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B1273" t="s">
         <v>1161</v>
@@ -15260,7 +15266,7 @@
     </row>
     <row r="1274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1274" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B1274" t="s">
         <v>1161</v>
@@ -15268,7 +15274,7 @@
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B1275" t="s">
         <v>1161</v>
@@ -15276,7 +15282,7 @@
     </row>
     <row r="1276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B1276" t="s">
         <v>1161</v>
@@ -15284,7 +15290,7 @@
     </row>
     <row r="1277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B1277" t="s">
         <v>1161</v>
@@ -15292,7 +15298,7 @@
     </row>
     <row r="1278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B1278" t="s">
         <v>1161</v>
@@ -15300,7 +15306,7 @@
     </row>
     <row r="1279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B1279" t="s">
         <v>1161</v>
@@ -15308,7 +15314,7 @@
     </row>
     <row r="1280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B1280" t="s">
         <v>1161</v>
@@ -15316,7 +15322,7 @@
     </row>
     <row r="1281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B1281" t="s">
         <v>1161</v>
@@ -15324,7 +15330,7 @@
     </row>
     <row r="1282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1282" t="s">
-        <v>604</v>
+        <v>1172</v>
       </c>
       <c r="B1282" t="s">
         <v>1161</v>
@@ -15332,7 +15338,7 @@
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
-        <v>1173</v>
+        <v>604</v>
       </c>
       <c r="B1283" t="s">
         <v>1161</v>
@@ -15340,7 +15346,7 @@
     </row>
     <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B1284" t="s">
         <v>1161</v>
@@ -15348,7 +15354,7 @@
     </row>
     <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1285" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B1285" t="s">
         <v>1161</v>
@@ -15356,7 +15362,7 @@
     </row>
     <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B1286" t="s">
         <v>1161</v>
@@ -15364,7 +15370,7 @@
     </row>
     <row r="1287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1287" t="s">
         <v>1161</v>
@@ -15372,7 +15378,7 @@
     </row>
     <row r="1288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1288" t="s">
         <v>1161</v>
@@ -15380,7 +15386,7 @@
     </row>
     <row r="1289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B1289" t="s">
         <v>1161</v>
@@ -15388,7 +15394,7 @@
     </row>
     <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1290" t="s">
-        <v>176</v>
+        <v>1179</v>
       </c>
       <c r="B1290" t="s">
         <v>1161</v>
@@ -15396,7 +15402,7 @@
     </row>
     <row r="1291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
-        <v>1180</v>
+        <v>176</v>
       </c>
       <c r="B1291" t="s">
         <v>1161</v>
@@ -15404,7 +15410,7 @@
     </row>
     <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B1292" t="s">
         <v>1161</v>
@@ -15412,7 +15418,7 @@
     </row>
     <row r="1293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1293" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B1293" t="s">
         <v>1161</v>
@@ -15420,7 +15426,7 @@
     </row>
     <row r="1294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1294" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B1294" t="s">
         <v>1161</v>
@@ -15428,7 +15434,7 @@
     </row>
     <row r="1295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1295" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B1295" t="s">
         <v>1161</v>
@@ -15436,7 +15442,7 @@
     </row>
     <row r="1296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B1296" t="s">
         <v>1161</v>
@@ -15444,7 +15450,7 @@
     </row>
     <row r="1297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1297" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B1297" t="s">
         <v>1161</v>
@@ -15452,7 +15458,7 @@
     </row>
     <row r="1298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1298" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B1298" t="s">
         <v>1161</v>
@@ -15460,7 +15466,7 @@
     </row>
     <row r="1299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B1299" t="s">
         <v>1161</v>
@@ -15468,7 +15474,7 @@
     </row>
     <row r="1300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B1300" t="s">
         <v>1161</v>
@@ -15476,7 +15482,7 @@
     </row>
     <row r="1301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
-        <v>924</v>
+        <v>1189</v>
       </c>
       <c r="B1301" t="s">
         <v>1161</v>
@@ -15484,7 +15490,7 @@
     </row>
     <row r="1302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
-        <v>710</v>
+        <v>924</v>
       </c>
       <c r="B1302" t="s">
         <v>1161</v>
@@ -15492,7 +15498,7 @@
     </row>
     <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>182</v>
+        <v>710</v>
       </c>
       <c r="B1303" t="s">
         <v>1161</v>
@@ -15500,7 +15506,7 @@
     </row>
     <row r="1304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="B1304" t="s">
         <v>1161</v>
@@ -15508,7 +15514,7 @@
     </row>
     <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
-        <v>683</v>
+        <v>25</v>
       </c>
       <c r="B1305" t="s">
         <v>1161</v>
@@ -15516,7 +15522,7 @@
     </row>
     <row r="1306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1306" t="s">
-        <v>305</v>
+        <v>683</v>
       </c>
       <c r="B1306" t="s">
         <v>1161</v>
@@ -15524,7 +15530,7 @@
     </row>
     <row r="1307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>185</v>
+        <v>305</v>
       </c>
       <c r="B1307" t="s">
         <v>1161</v>
@@ -15532,7 +15538,7 @@
     </row>
     <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>1190</v>
+        <v>185</v>
       </c>
       <c r="B1308" t="s">
         <v>1161</v>
@@ -15540,7 +15546,7 @@
     </row>
     <row r="1309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B1309" t="s">
         <v>1161</v>
@@ -15548,7 +15554,7 @@
     </row>
     <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B1310" t="s">
         <v>1161</v>
@@ -15556,7 +15562,7 @@
     </row>
     <row r="1311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B1311" t="s">
         <v>1161</v>
@@ -15564,7 +15570,7 @@
     </row>
     <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B1312" t="s">
         <v>1161</v>
@@ -15572,15 +15578,15 @@
     </row>
     <row r="1313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1313" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B1313" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="1314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1314" s="4" t="s">
-        <v>1196</v>
+      <c r="A1314" t="s">
+        <v>1195</v>
       </c>
       <c r="B1314" t="s">
         <v>1161</v>
@@ -15588,15 +15594,15 @@
     </row>
     <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B1315" t="s">
-        <v>277</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B1316" t="s">
         <v>277</v>
@@ -15604,7 +15610,7 @@
     </row>
     <row r="1317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B1317" t="s">
         <v>277</v>
@@ -15612,7 +15618,7 @@
     </row>
     <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>30</v>
+        <v>1199</v>
       </c>
       <c r="B1318" t="s">
         <v>277</v>
@@ -15620,7 +15626,7 @@
     </row>
     <row r="1319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="B1319" t="s">
         <v>277</v>
@@ -15628,7 +15634,7 @@
     </row>
     <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B1320" t="s">
         <v>277</v>
@@ -15636,7 +15642,7 @@
     </row>
     <row r="1321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>1503</v>
+        <v>1201</v>
       </c>
       <c r="B1321" t="s">
         <v>277</v>
@@ -15644,7 +15650,7 @@
     </row>
     <row r="1322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>1203</v>
+        <v>1503</v>
       </c>
       <c r="B1322" t="s">
         <v>277</v>
@@ -15652,7 +15658,7 @@
     </row>
     <row r="1323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
-        <v>9</v>
+        <v>1203</v>
       </c>
       <c r="B1323" t="s">
         <v>277</v>
@@ -15660,7 +15666,7 @@
     </row>
     <row r="1324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>1204</v>
+        <v>9</v>
       </c>
       <c r="B1324" t="s">
         <v>277</v>
@@ -15668,7 +15674,7 @@
     </row>
     <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B1325" t="s">
         <v>277</v>
@@ -15676,7 +15682,7 @@
     </row>
     <row r="1326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B1326" t="s">
         <v>277</v>
@@ -15684,7 +15690,7 @@
     </row>
     <row r="1327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B1327" t="s">
         <v>277</v>
@@ -15692,7 +15698,7 @@
     </row>
     <row r="1328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
-        <v>1176</v>
+        <v>1207</v>
       </c>
       <c r="B1328" t="s">
         <v>277</v>
@@ -15700,7 +15706,7 @@
     </row>
     <row r="1329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
-        <v>1208</v>
+        <v>1176</v>
       </c>
       <c r="B1329" t="s">
         <v>277</v>
@@ -15708,7 +15714,7 @@
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B1330" t="s">
         <v>277</v>
@@ -15716,7 +15722,7 @@
     </row>
     <row r="1331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B1331" t="s">
         <v>277</v>
@@ -15724,7 +15730,7 @@
     </row>
     <row r="1332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B1332" t="s">
         <v>277</v>
@@ -15732,7 +15738,7 @@
     </row>
     <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B1333" t="s">
         <v>277</v>
@@ -15740,7 +15746,7 @@
     </row>
     <row r="1334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B1334" t="s">
         <v>277</v>
@@ -15748,7 +15754,7 @@
     </row>
     <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B1335" t="s">
         <v>277</v>
@@ -15756,7 +15762,7 @@
     </row>
     <row r="1336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B1336" t="s">
         <v>277</v>
@@ -15764,7 +15770,7 @@
     </row>
     <row r="1337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B1337" t="s">
         <v>277</v>
@@ -15772,7 +15778,7 @@
     </row>
     <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B1338" t="s">
         <v>277</v>
@@ -15780,7 +15786,7 @@
     </row>
     <row r="1339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1339" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B1339" t="s">
         <v>277</v>
@@ -15788,7 +15794,7 @@
     </row>
     <row r="1340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B1340" t="s">
         <v>277</v>
@@ -15796,7 +15802,7 @@
     </row>
     <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B1341" t="s">
         <v>277</v>
@@ -15804,7 +15810,7 @@
     </row>
     <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
-        <v>300</v>
+        <v>1220</v>
       </c>
       <c r="B1342" t="s">
         <v>277</v>
@@ -15812,7 +15818,7 @@
     </row>
     <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
-        <v>1221</v>
+        <v>300</v>
       </c>
       <c r="B1343" t="s">
         <v>277</v>
@@ -15820,7 +15826,7 @@
     </row>
     <row r="1344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
-        <v>277</v>
+        <v>1221</v>
       </c>
       <c r="B1344" t="s">
         <v>277</v>
@@ -15828,7 +15834,7 @@
     </row>
     <row r="1345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
-        <v>1222</v>
+        <v>277</v>
       </c>
       <c r="B1345" t="s">
         <v>277</v>
@@ -15836,7 +15842,7 @@
     </row>
     <row r="1346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B1346" t="s">
         <v>277</v>
@@ -15844,7 +15850,7 @@
     </row>
     <row r="1347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1347" t="s">
-        <v>411</v>
+        <v>1223</v>
       </c>
       <c r="B1347" t="s">
         <v>277</v>
@@ -15852,7 +15858,7 @@
     </row>
     <row r="1348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1348" t="s">
-        <v>1056</v>
+        <v>411</v>
       </c>
       <c r="B1348" t="s">
         <v>277</v>
@@ -15860,7 +15866,7 @@
     </row>
     <row r="1349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
-        <v>50</v>
+        <v>1056</v>
       </c>
       <c r="B1349" t="s">
         <v>277</v>
@@ -15868,7 +15874,7 @@
     </row>
     <row r="1350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
-        <v>1224</v>
+        <v>50</v>
       </c>
       <c r="B1350" t="s">
         <v>277</v>
@@ -15876,7 +15882,7 @@
     </row>
     <row r="1351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1351" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B1351" t="s">
         <v>277</v>
@@ -15884,7 +15890,7 @@
     </row>
     <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1352" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B1352" t="s">
         <v>277</v>
@@ -15892,7 +15898,7 @@
     </row>
     <row r="1353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B1353" t="s">
         <v>277</v>
@@ -15900,7 +15906,7 @@
     </row>
     <row r="1354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B1354" t="s">
         <v>277</v>
@@ -15908,7 +15914,7 @@
     </row>
     <row r="1355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1355" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B1355" t="s">
         <v>277</v>
@@ -15916,15 +15922,15 @@
     </row>
     <row r="1356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1356" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B1356" t="s">
-        <v>634</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B1357" t="s">
         <v>634</v>
@@ -15932,7 +15938,7 @@
     </row>
     <row r="1358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B1358" t="s">
         <v>634</v>
@@ -15940,7 +15946,7 @@
     </row>
     <row r="1359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B1359" t="s">
         <v>634</v>
@@ -15948,7 +15954,7 @@
     </row>
     <row r="1360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1360" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B1360" t="s">
         <v>634</v>
@@ -15956,7 +15962,7 @@
     </row>
     <row r="1361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B1361" t="s">
         <v>634</v>
@@ -15964,15 +15970,15 @@
     </row>
     <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B1362" t="s">
-        <v>327</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1363" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B1363" t="s">
         <v>327</v>
@@ -15980,7 +15986,7 @@
     </row>
     <row r="1364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1364" t="s">
-        <v>407</v>
+        <v>1237</v>
       </c>
       <c r="B1364" t="s">
         <v>327</v>
@@ -15988,7 +15994,7 @@
     </row>
     <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
-        <v>1238</v>
+        <v>407</v>
       </c>
       <c r="B1365" t="s">
         <v>327</v>
@@ -15996,7 +16002,7 @@
     </row>
     <row r="1366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B1366" t="s">
         <v>327</v>
@@ -16004,7 +16010,7 @@
     </row>
     <row r="1367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1367" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B1367" t="s">
         <v>327</v>
@@ -16012,7 +16018,7 @@
     </row>
     <row r="1368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1368" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B1368" t="s">
         <v>327</v>
@@ -16020,7 +16026,7 @@
     </row>
     <row r="1369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
-        <v>150</v>
+        <v>1241</v>
       </c>
       <c r="B1369" t="s">
         <v>327</v>
@@ -16028,7 +16034,7 @@
     </row>
     <row r="1370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
-        <v>1242</v>
+        <v>150</v>
       </c>
       <c r="B1370" t="s">
         <v>327</v>
@@ -16036,7 +16042,7 @@
     </row>
     <row r="1371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1371" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B1371" t="s">
         <v>327</v>
@@ -16044,7 +16050,7 @@
     </row>
     <row r="1372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1372" t="s">
-        <v>712</v>
+        <v>1243</v>
       </c>
       <c r="B1372" t="s">
         <v>327</v>
@@ -16052,7 +16058,7 @@
     </row>
     <row r="1373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
-        <v>1244</v>
+        <v>712</v>
       </c>
       <c r="B1373" t="s">
         <v>327</v>
@@ -16060,7 +16066,7 @@
     </row>
     <row r="1374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
-        <v>1140</v>
+        <v>1244</v>
       </c>
       <c r="B1374" t="s">
         <v>327</v>
@@ -16068,7 +16074,7 @@
     </row>
     <row r="1375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1375" t="s">
-        <v>1245</v>
+        <v>1140</v>
       </c>
       <c r="B1375" t="s">
         <v>327</v>
@@ -16076,15 +16082,15 @@
     </row>
     <row r="1376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1376" t="s">
-        <v>436</v>
+        <v>1245</v>
       </c>
       <c r="B1376" t="s">
-        <v>1246</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1377" t="s">
-        <v>1247</v>
+        <v>436</v>
       </c>
       <c r="B1377" t="s">
         <v>1246</v>
@@ -16092,7 +16098,7 @@
     </row>
     <row r="1378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B1378" t="s">
         <v>1246</v>
@@ -16100,7 +16106,7 @@
     </row>
     <row r="1379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1379" t="s">
-        <v>995</v>
+        <v>1248</v>
       </c>
       <c r="B1379" t="s">
         <v>1246</v>
@@ -16108,7 +16114,7 @@
     </row>
     <row r="1380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1380" t="s">
-        <v>660</v>
+        <v>995</v>
       </c>
       <c r="B1380" t="s">
         <v>1246</v>
@@ -16116,7 +16122,7 @@
     </row>
     <row r="1381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1381" t="s">
-        <v>1249</v>
+        <v>660</v>
       </c>
       <c r="B1381" t="s">
         <v>1246</v>
@@ -16124,7 +16130,7 @@
     </row>
     <row r="1382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B1382" t="s">
         <v>1246</v>
@@ -16132,7 +16138,7 @@
     </row>
     <row r="1383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1383" t="s">
-        <v>1102</v>
+        <v>1250</v>
       </c>
       <c r="B1383" t="s">
         <v>1246</v>
@@ -16140,7 +16146,7 @@
     </row>
     <row r="1384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
-        <v>1251</v>
+        <v>1102</v>
       </c>
       <c r="B1384" t="s">
         <v>1246</v>
@@ -16148,7 +16154,7 @@
     </row>
     <row r="1385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B1385" t="s">
         <v>1246</v>
@@ -16156,7 +16162,7 @@
     </row>
     <row r="1386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="B1386" t="s">
         <v>1246</v>
@@ -16164,7 +16170,7 @@
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1387" t="s">
-        <v>708</v>
+        <v>1246</v>
       </c>
       <c r="B1387" t="s">
         <v>1246</v>
@@ -16172,7 +16178,7 @@
     </row>
     <row r="1388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1388" t="s">
-        <v>411</v>
+        <v>708</v>
       </c>
       <c r="B1388" t="s">
         <v>1246</v>
@@ -16180,7 +16186,7 @@
     </row>
     <row r="1389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
-        <v>278</v>
+        <v>411</v>
       </c>
       <c r="B1389" t="s">
         <v>1246</v>
@@ -16188,7 +16194,7 @@
     </row>
     <row r="1390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="B1390" t="s">
         <v>1246</v>
@@ -16196,7 +16202,7 @@
     </row>
     <row r="1391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1391" t="s">
-        <v>474</v>
+        <v>181</v>
       </c>
       <c r="B1391" t="s">
         <v>1246</v>
@@ -16204,7 +16210,7 @@
     </row>
     <row r="1392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1392" t="s">
-        <v>305</v>
+        <v>474</v>
       </c>
       <c r="B1392" t="s">
         <v>1246</v>
@@ -16212,15 +16218,15 @@
     </row>
     <row r="1393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
-        <v>1253</v>
+        <v>305</v>
       </c>
       <c r="B1393" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="1394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B1394" t="s">
         <v>1254</v>
@@ -16228,7 +16234,7 @@
     </row>
     <row r="1395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B1395" t="s">
         <v>1254</v>
@@ -16236,7 +16242,7 @@
     </row>
     <row r="1396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B1396" t="s">
         <v>1254</v>
@@ -16244,7 +16250,7 @@
     </row>
     <row r="1397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B1397" t="s">
         <v>1254</v>
@@ -16252,7 +16258,7 @@
     </row>
     <row r="1398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B1398" t="s">
         <v>1254</v>
@@ -16260,7 +16266,7 @@
     </row>
     <row r="1399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B1399" t="s">
         <v>1254</v>
@@ -16268,7 +16274,7 @@
     </row>
     <row r="1400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B1400" t="s">
         <v>1254</v>
@@ -16276,7 +16282,7 @@
     </row>
     <row r="1401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B1401" t="s">
         <v>1254</v>
@@ -16284,7 +16290,7 @@
     </row>
     <row r="1402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B1402" t="s">
         <v>1254</v>
@@ -16292,7 +16298,7 @@
     </row>
     <row r="1403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B1403" t="s">
         <v>1254</v>
@@ -16300,7 +16306,7 @@
     </row>
     <row r="1404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B1404" t="s">
         <v>1254</v>
@@ -16308,7 +16314,7 @@
     </row>
     <row r="1405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B1405" t="s">
         <v>1254</v>
@@ -16316,7 +16322,7 @@
     </row>
     <row r="1406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B1406" t="s">
         <v>1254</v>
@@ -16324,7 +16330,7 @@
     </row>
     <row r="1407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B1407" t="s">
         <v>1254</v>
@@ -16332,7 +16338,7 @@
     </row>
     <row r="1408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B1408" t="s">
         <v>1254</v>
@@ -16340,7 +16346,7 @@
     </row>
     <row r="1409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B1409" t="s">
         <v>1254</v>
@@ -16348,7 +16354,7 @@
     </row>
     <row r="1410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B1410" t="s">
         <v>1254</v>
@@ -16356,7 +16362,7 @@
     </row>
     <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B1411" t="s">
         <v>1254</v>
@@ -16364,7 +16370,7 @@
     </row>
     <row r="1412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
-        <v>1158</v>
+        <v>1272</v>
       </c>
       <c r="B1412" t="s">
         <v>1254</v>
@@ -16372,7 +16378,7 @@
     </row>
     <row r="1413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
-        <v>331</v>
+        <v>1158</v>
       </c>
       <c r="B1413" t="s">
         <v>1254</v>
@@ -16380,7 +16386,7 @@
     </row>
     <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>1273</v>
+        <v>331</v>
       </c>
       <c r="B1414" t="s">
         <v>1254</v>
@@ -16388,7 +16394,7 @@
     </row>
     <row r="1415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1415" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B1415" t="s">
         <v>1254</v>
@@ -16396,23 +16402,23 @@
     </row>
     <row r="1416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1416" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B1416" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="1417" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1417" s="4" t="s">
-        <v>1276</v>
+      <c r="A1417" t="s">
+        <v>1275</v>
       </c>
       <c r="B1417" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1418" s="4" t="s">
-        <v>1277</v>
+      <c r="A1418" t="s">
+        <v>1276</v>
       </c>
       <c r="B1418" t="s">
         <v>1254</v>
@@ -16420,15 +16426,15 @@
     </row>
     <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1419" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B1419" t="s">
-        <v>540</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B1420" t="s">
         <v>540</v>
@@ -16436,7 +16442,7 @@
     </row>
     <row r="1421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B1421" t="s">
         <v>540</v>
@@ -16444,7 +16450,7 @@
     </row>
     <row r="1422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B1422" t="s">
         <v>540</v>
@@ -16452,7 +16458,7 @@
     </row>
     <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B1423" t="s">
         <v>540</v>
@@ -16460,7 +16466,7 @@
     </row>
     <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B1424" t="s">
         <v>540</v>
@@ -16468,7 +16474,7 @@
     </row>
     <row r="1425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B1425" t="s">
         <v>540</v>
@@ -16476,15 +16482,15 @@
     </row>
     <row r="1426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B1426" t="s">
-        <v>1286</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B1427" t="s">
         <v>1286</v>
@@ -16492,7 +16498,7 @@
     </row>
     <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B1428" t="s">
         <v>1286</v>
@@ -16500,7 +16506,7 @@
     </row>
     <row r="1429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1429" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B1429" t="s">
         <v>1286</v>
@@ -16508,7 +16514,7 @@
     </row>
     <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>24</v>
+        <v>1289</v>
       </c>
       <c r="B1430" t="s">
         <v>1286</v>
@@ -16516,7 +16522,7 @@
     </row>
     <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1431" t="s">
-        <v>1290</v>
+        <v>24</v>
       </c>
       <c r="B1431" t="s">
         <v>1286</v>
@@ -16524,15 +16530,15 @@
     </row>
     <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B1432" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1433" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B1433" t="s">
         <v>1292</v>
@@ -16540,7 +16546,7 @@
     </row>
     <row r="1434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B1434" t="s">
         <v>1292</v>
@@ -16548,7 +16554,7 @@
     </row>
     <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1435" t="s">
-        <v>1504</v>
+        <v>1294</v>
       </c>
       <c r="B1435" t="s">
         <v>1292</v>
@@ -16556,7 +16562,7 @@
     </row>
     <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>1295</v>
+        <v>1504</v>
       </c>
       <c r="B1436" t="s">
         <v>1292</v>
@@ -16564,7 +16570,7 @@
     </row>
     <row r="1437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1437" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B1437" t="s">
         <v>1292</v>
@@ -16572,7 +16578,7 @@
     </row>
     <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B1438" t="s">
         <v>1292</v>
@@ -16580,7 +16586,7 @@
     </row>
     <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B1439" t="s">
         <v>1292</v>
@@ -16588,7 +16594,7 @@
     </row>
     <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B1440" t="s">
         <v>1292</v>
@@ -16596,7 +16602,7 @@
     </row>
     <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1441" t="s">
-        <v>38</v>
+        <v>1299</v>
       </c>
       <c r="B1441" t="s">
         <v>1292</v>
@@ -16604,7 +16610,7 @@
     </row>
     <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
-        <v>1300</v>
+        <v>38</v>
       </c>
       <c r="B1442" t="s">
         <v>1292</v>
@@ -16612,7 +16618,7 @@
     </row>
     <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1443" t="s">
-        <v>21</v>
+        <v>1300</v>
       </c>
       <c r="B1443" t="s">
         <v>1292</v>
@@ -16620,7 +16626,7 @@
     </row>
     <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1444" t="s">
-        <v>1301</v>
+        <v>21</v>
       </c>
       <c r="B1444" t="s">
         <v>1292</v>
@@ -16628,7 +16634,7 @@
     </row>
     <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1445" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B1445" t="s">
         <v>1292</v>
@@ -16636,7 +16642,7 @@
     </row>
     <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B1446" t="s">
         <v>1292</v>
@@ -16644,15 +16650,15 @@
     </row>
     <row r="1447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1447" t="s">
-        <v>60</v>
+        <v>1303</v>
       </c>
       <c r="B1447" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1448" t="s">
-        <v>1305</v>
+        <v>60</v>
       </c>
       <c r="B1448" t="s">
         <v>1304</v>
@@ -16660,7 +16666,7 @@
     </row>
     <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1449" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B1449" t="s">
         <v>1304</v>
@@ -16668,7 +16674,7 @@
     </row>
     <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B1450" t="s">
         <v>1304</v>
@@ -16676,7 +16682,7 @@
     </row>
     <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1451" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B1451" t="s">
         <v>1304</v>
@@ -16684,7 +16690,7 @@
     </row>
     <row r="1452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1452" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B1452" t="s">
         <v>1304</v>
@@ -16692,7 +16698,7 @@
     </row>
     <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1453" t="s">
-        <v>331</v>
+        <v>1309</v>
       </c>
       <c r="B1453" t="s">
         <v>1304</v>
@@ -16700,7 +16706,7 @@
     </row>
     <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>1310</v>
+        <v>331</v>
       </c>
       <c r="B1454" t="s">
         <v>1304</v>
@@ -16708,7 +16714,7 @@
     </row>
     <row r="1455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1455" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B1455" t="s">
         <v>1304</v>
@@ -16716,7 +16722,7 @@
     </row>
     <row r="1456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1456" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B1456" t="s">
         <v>1304</v>
@@ -16724,7 +16730,7 @@
     </row>
     <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B1457" t="s">
         <v>1304</v>
@@ -16732,7 +16738,7 @@
     </row>
     <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="B1458" t="s">
         <v>1304</v>
@@ -16740,15 +16746,15 @@
     </row>
     <row r="1459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1459" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B1459" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="1460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1460" t="s">
-        <v>983</v>
+        <v>1315</v>
       </c>
       <c r="B1460" t="s">
         <v>1316</v>
@@ -16756,7 +16762,7 @@
     </row>
     <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1461" t="s">
-        <v>1317</v>
+        <v>983</v>
       </c>
       <c r="B1461" t="s">
         <v>1316</v>
@@ -16764,7 +16770,7 @@
     </row>
     <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1462" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B1462" t="s">
         <v>1316</v>
@@ -16772,7 +16778,7 @@
     </row>
     <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1463" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B1463" t="s">
         <v>1316</v>
@@ -16780,7 +16786,7 @@
     </row>
     <row r="1464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1464" t="s">
-        <v>461</v>
+        <v>1319</v>
       </c>
       <c r="B1464" t="s">
         <v>1316</v>
@@ -16788,7 +16794,7 @@
     </row>
     <row r="1465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1465" t="s">
-        <v>1320</v>
+        <v>461</v>
       </c>
       <c r="B1465" t="s">
         <v>1316</v>
@@ -16796,7 +16802,7 @@
     </row>
     <row r="1466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1466" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B1466" t="s">
         <v>1316</v>
@@ -16804,7 +16810,7 @@
     </row>
     <row r="1467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1467" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B1467" t="s">
         <v>1316</v>
@@ -16812,7 +16818,7 @@
     </row>
     <row r="1468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1468" t="s">
-        <v>273</v>
+        <v>1322</v>
       </c>
       <c r="B1468" t="s">
         <v>1316</v>
@@ -16820,7 +16826,7 @@
     </row>
     <row r="1469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1469" t="s">
-        <v>1215</v>
+        <v>273</v>
       </c>
       <c r="B1469" t="s">
         <v>1316</v>
@@ -16828,7 +16834,7 @@
     </row>
     <row r="1470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1470" t="s">
-        <v>1323</v>
+        <v>1215</v>
       </c>
       <c r="B1470" t="s">
         <v>1316</v>
@@ -16836,7 +16842,7 @@
     </row>
     <row r="1471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1471" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B1471" t="s">
         <v>1316</v>
@@ -16844,7 +16850,7 @@
     </row>
     <row r="1472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1472" t="s">
-        <v>50</v>
+        <v>1324</v>
       </c>
       <c r="B1472" t="s">
         <v>1316</v>
@@ -16852,7 +16858,7 @@
     </row>
     <row r="1473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1473" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B1473" t="s">
         <v>1316</v>
@@ -16860,7 +16866,7 @@
     </row>
     <row r="1474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1474" t="s">
-        <v>1325</v>
+        <v>24</v>
       </c>
       <c r="B1474" t="s">
         <v>1316</v>
@@ -16868,7 +16874,7 @@
     </row>
     <row r="1475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1475" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B1475" t="s">
         <v>1316</v>
@@ -16876,7 +16882,7 @@
     </row>
     <row r="1476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1476" t="s">
-        <v>477</v>
+        <v>1326</v>
       </c>
       <c r="B1476" t="s">
         <v>1316</v>
@@ -16884,7 +16890,7 @@
     </row>
     <row r="1477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1477" t="s">
-        <v>1327</v>
+        <v>477</v>
       </c>
       <c r="B1477" t="s">
         <v>1316</v>
@@ -16892,15 +16898,15 @@
     </row>
     <row r="1478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1478" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B1478" t="s">
-        <v>875</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1479" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B1479" t="s">
         <v>875</v>
@@ -16908,7 +16914,7 @@
     </row>
     <row r="1480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1480" t="s">
-        <v>46</v>
+        <v>1329</v>
       </c>
       <c r="B1480" t="s">
         <v>875</v>
@@ -16916,7 +16922,7 @@
     </row>
     <row r="1481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1481" t="s">
-        <v>1330</v>
+        <v>46</v>
       </c>
       <c r="B1481" t="s">
         <v>875</v>
@@ -16924,7 +16930,7 @@
     </row>
     <row r="1482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B1482" t="s">
         <v>875</v>
@@ -16932,7 +16938,7 @@
     </row>
     <row r="1483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1483" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B1483" t="s">
         <v>875</v>
@@ -16940,7 +16946,7 @@
     </row>
     <row r="1484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1484" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B1484" t="s">
         <v>875</v>
@@ -16948,7 +16954,7 @@
     </row>
     <row r="1485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1485" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B1485" t="s">
         <v>875</v>
@@ -16956,7 +16962,7 @@
     </row>
     <row r="1486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1486" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B1486" t="s">
         <v>875</v>
@@ -16964,7 +16970,7 @@
     </row>
     <row r="1487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1487" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B1487" t="s">
         <v>875</v>
@@ -16972,7 +16978,7 @@
     </row>
     <row r="1488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1488" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B1488" t="s">
         <v>875</v>
@@ -16980,7 +16986,7 @@
     </row>
     <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B1489" t="s">
         <v>875</v>
@@ -16988,15 +16994,15 @@
     </row>
     <row r="1490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B1490" t="s">
-        <v>1340</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B1491" t="s">
         <v>1340</v>
@@ -17004,7 +17010,7 @@
     </row>
     <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B1492" t="s">
         <v>1340</v>
@@ -17012,7 +17018,7 @@
     </row>
     <row r="1493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B1493" t="s">
         <v>1340</v>
@@ -17020,7 +17026,7 @@
     </row>
     <row r="1494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B1494" t="s">
         <v>1340</v>
@@ -17028,7 +17034,7 @@
     </row>
     <row r="1495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B1495" t="s">
         <v>1340</v>
@@ -17036,7 +17042,7 @@
     </row>
     <row r="1496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B1496" t="s">
         <v>1340</v>
@@ -17044,7 +17050,7 @@
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B1497" t="s">
         <v>1340</v>
@@ -17052,7 +17058,7 @@
     </row>
     <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B1498" t="s">
         <v>1340</v>
@@ -17060,7 +17066,7 @@
     </row>
     <row r="1499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B1499" t="s">
         <v>1340</v>
@@ -17068,7 +17074,7 @@
     </row>
     <row r="1500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B1500" t="s">
         <v>1340</v>
@@ -17076,7 +17082,7 @@
     </row>
     <row r="1501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B1501" t="s">
         <v>1340</v>
@@ -17084,7 +17090,7 @@
     </row>
     <row r="1502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B1502" t="s">
         <v>1340</v>
@@ -17092,7 +17098,7 @@
     </row>
     <row r="1503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
-        <v>874</v>
+        <v>1352</v>
       </c>
       <c r="B1503" t="s">
         <v>1340</v>
@@ -17100,7 +17106,7 @@
     </row>
     <row r="1504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
-        <v>1353</v>
+        <v>874</v>
       </c>
       <c r="B1504" t="s">
         <v>1340</v>
@@ -17108,7 +17114,7 @@
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1505" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B1505" t="s">
         <v>1340</v>
@@ -17116,7 +17122,7 @@
     </row>
     <row r="1506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B1506" t="s">
         <v>1340</v>
@@ -17124,7 +17130,7 @@
     </row>
     <row r="1507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1507" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B1507" t="s">
         <v>1340</v>
@@ -17132,7 +17138,7 @@
     </row>
     <row r="1508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1508" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B1508" t="s">
         <v>1340</v>
@@ -17140,15 +17146,15 @@
     </row>
     <row r="1509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1509" t="s">
-        <v>439</v>
+        <v>1357</v>
       </c>
       <c r="B1509" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="1510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1510" t="s">
-        <v>1359</v>
+        <v>439</v>
       </c>
       <c r="B1510" t="s">
         <v>1358</v>
@@ -17156,7 +17162,7 @@
     </row>
     <row r="1511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1511" t="s">
-        <v>604</v>
+        <v>1359</v>
       </c>
       <c r="B1511" t="s">
         <v>1358</v>
@@ -17164,7 +17170,7 @@
     </row>
     <row r="1512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1512" t="s">
-        <v>1360</v>
+        <v>604</v>
       </c>
       <c r="B1512" t="s">
         <v>1358</v>
@@ -17172,7 +17178,7 @@
     </row>
     <row r="1513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1513" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B1513" t="s">
         <v>1358</v>
@@ -17180,7 +17186,7 @@
     </row>
     <row r="1514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1514" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B1514" t="s">
         <v>1358</v>
@@ -17188,7 +17194,7 @@
     </row>
     <row r="1515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1515" t="s">
-        <v>1204</v>
+        <v>1362</v>
       </c>
       <c r="B1515" t="s">
         <v>1358</v>
@@ -17196,7 +17202,7 @@
     </row>
     <row r="1516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1516" t="s">
-        <v>1363</v>
+        <v>1204</v>
       </c>
       <c r="B1516" t="s">
         <v>1358</v>
@@ -17204,7 +17210,7 @@
     </row>
     <row r="1517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1517" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B1517" t="s">
         <v>1358</v>
@@ -17212,7 +17218,7 @@
     </row>
     <row r="1518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1518" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B1518" t="s">
         <v>1358</v>
@@ -17220,7 +17226,7 @@
     </row>
     <row r="1519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1519" t="s">
-        <v>21</v>
+        <v>1365</v>
       </c>
       <c r="B1519" t="s">
         <v>1358</v>
@@ -17228,7 +17234,7 @@
     </row>
     <row r="1520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1520" t="s">
-        <v>923</v>
+        <v>21</v>
       </c>
       <c r="B1520" t="s">
         <v>1358</v>
@@ -17236,7 +17242,7 @@
     </row>
     <row r="1521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1521" t="s">
-        <v>1366</v>
+        <v>923</v>
       </c>
       <c r="B1521" t="s">
         <v>1358</v>
@@ -17244,7 +17250,7 @@
     </row>
     <row r="1522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1522" t="s">
-        <v>50</v>
+        <v>1366</v>
       </c>
       <c r="B1522" t="s">
         <v>1358</v>
@@ -17252,7 +17258,7 @@
     </row>
     <row r="1523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B1523" t="s">
         <v>1358</v>
@@ -17260,7 +17266,7 @@
     </row>
     <row r="1524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
-        <v>1367</v>
+        <v>23</v>
       </c>
       <c r="B1524" t="s">
         <v>1358</v>
@@ -17268,7 +17274,7 @@
     </row>
     <row r="1525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1525" t="s">
-        <v>1190</v>
+        <v>1367</v>
       </c>
       <c r="B1525" t="s">
         <v>1358</v>
@@ -17276,7 +17282,7 @@
     </row>
     <row r="1526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
-        <v>1121</v>
+        <v>1190</v>
       </c>
       <c r="B1526" t="s">
         <v>1358</v>
@@ -17284,7 +17290,7 @@
     </row>
     <row r="1527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1527" t="s">
-        <v>1368</v>
+        <v>1121</v>
       </c>
       <c r="B1527" t="s">
         <v>1358</v>
@@ -17292,7 +17298,7 @@
     </row>
     <row r="1528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1528" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B1528" t="s">
         <v>1358</v>
@@ -17300,7 +17306,7 @@
     </row>
     <row r="1529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1529" t="s">
-        <v>787</v>
+        <v>1369</v>
       </c>
       <c r="B1529" t="s">
         <v>1358</v>
@@ -17308,15 +17314,15 @@
     </row>
     <row r="1530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
-        <v>1370</v>
+        <v>787</v>
       </c>
       <c r="B1530" t="s">
-        <v>1371</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="1531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B1531" t="s">
         <v>1371</v>
@@ -17324,7 +17330,7 @@
     </row>
     <row r="1532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B1532" t="s">
         <v>1371</v>
@@ -17332,7 +17338,7 @@
     </row>
     <row r="1533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1533" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B1533" t="s">
         <v>1371</v>
@@ -17340,7 +17346,7 @@
     </row>
     <row r="1534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1534" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B1534" t="s">
         <v>1371</v>
@@ -17348,7 +17354,7 @@
     </row>
     <row r="1535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1535" t="s">
-        <v>34</v>
+        <v>1375</v>
       </c>
       <c r="B1535" t="s">
         <v>1371</v>
@@ -17356,7 +17362,7 @@
     </row>
     <row r="1536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1536" t="s">
-        <v>1376</v>
+        <v>34</v>
       </c>
       <c r="B1536" t="s">
         <v>1371</v>
@@ -17364,7 +17370,7 @@
     </row>
     <row r="1537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1537" t="s">
-        <v>230</v>
+        <v>1376</v>
       </c>
       <c r="B1537" t="s">
         <v>1371</v>
@@ -17372,7 +17378,7 @@
     </row>
     <row r="1538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1538" t="s">
-        <v>1377</v>
+        <v>230</v>
       </c>
       <c r="B1538" t="s">
         <v>1371</v>
@@ -17380,7 +17386,7 @@
     </row>
     <row r="1539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1539" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B1539" t="s">
         <v>1371</v>
@@ -17388,7 +17394,7 @@
     </row>
     <row r="1540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1540" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B1540" t="s">
         <v>1371</v>
@@ -17396,7 +17402,7 @@
     </row>
     <row r="1541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1541" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B1541" t="s">
         <v>1371</v>
@@ -17404,7 +17410,7 @@
     </row>
     <row r="1542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B1542" t="s">
         <v>1371</v>
@@ -17412,7 +17418,7 @@
     </row>
     <row r="1543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B1543" t="s">
         <v>1371</v>
@@ -17420,7 +17426,7 @@
     </row>
     <row r="1544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1544" t="s">
-        <v>708</v>
+        <v>1382</v>
       </c>
       <c r="B1544" t="s">
         <v>1371</v>
@@ -17428,7 +17434,7 @@
     </row>
     <row r="1545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1545" t="s">
-        <v>249</v>
+        <v>708</v>
       </c>
       <c r="B1545" t="s">
         <v>1371</v>
@@ -17436,7 +17442,7 @@
     </row>
     <row r="1546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1546" t="s">
-        <v>1383</v>
+        <v>249</v>
       </c>
       <c r="B1546" t="s">
         <v>1371</v>
@@ -17444,7 +17450,7 @@
     </row>
     <row r="1547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1547" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1547" t="s">
         <v>1371</v>
@@ -17452,7 +17458,7 @@
     </row>
     <row r="1548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B1548" t="s">
         <v>1371</v>
@@ -17460,15 +17466,15 @@
     </row>
     <row r="1549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1549" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B1549" t="s">
-        <v>1387</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="1550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1550" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B1550" t="s">
         <v>1387</v>
@@ -17476,7 +17482,7 @@
     </row>
     <row r="1551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1551" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B1551" t="s">
         <v>1387</v>
@@ -17484,7 +17490,7 @@
     </row>
     <row r="1552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1552" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B1552" t="s">
         <v>1387</v>
@@ -17492,7 +17498,7 @@
     </row>
     <row r="1553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
-        <v>660</v>
+        <v>1390</v>
       </c>
       <c r="B1553" t="s">
         <v>1387</v>
@@ -17500,7 +17506,7 @@
     </row>
     <row r="1554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1554" t="s">
-        <v>1391</v>
+        <v>660</v>
       </c>
       <c r="B1554" t="s">
         <v>1387</v>
@@ -17508,7 +17514,7 @@
     </row>
     <row r="1555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1555" t="s">
-        <v>10</v>
+        <v>1391</v>
       </c>
       <c r="B1555" t="s">
         <v>1387</v>
@@ -17516,7 +17522,7 @@
     </row>
     <row r="1556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1556" t="s">
-        <v>1392</v>
+        <v>10</v>
       </c>
       <c r="B1556" t="s">
         <v>1387</v>
@@ -17524,7 +17530,7 @@
     </row>
     <row r="1557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1557" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B1557" t="s">
         <v>1387</v>
@@ -17532,7 +17538,7 @@
     </row>
     <row r="1558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1558" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B1558" t="s">
         <v>1387</v>
@@ -17540,7 +17546,7 @@
     </row>
     <row r="1559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1559" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1559" t="s">
         <v>1387</v>
@@ -17548,7 +17554,7 @@
     </row>
     <row r="1560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1560" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1560" t="s">
         <v>1387</v>
@@ -17556,7 +17562,7 @@
     </row>
     <row r="1561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1561" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B1561" t="s">
         <v>1387</v>
@@ -17564,7 +17570,7 @@
     </row>
     <row r="1562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1562" t="s">
-        <v>181</v>
+        <v>1397</v>
       </c>
       <c r="B1562" t="s">
         <v>1387</v>
@@ -17572,7 +17578,7 @@
     </row>
     <row r="1563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1563" t="s">
-        <v>710</v>
+        <v>181</v>
       </c>
       <c r="B1563" t="s">
         <v>1387</v>
@@ -17580,7 +17586,7 @@
     </row>
     <row r="1564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1564" t="s">
-        <v>1398</v>
+        <v>710</v>
       </c>
       <c r="B1564" t="s">
         <v>1387</v>
@@ -17588,7 +17594,7 @@
     </row>
     <row r="1565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B1565" t="s">
         <v>1387</v>
@@ -17596,7 +17602,7 @@
     </row>
     <row r="1566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1566" t="s">
-        <v>764</v>
+        <v>1399</v>
       </c>
       <c r="B1566" t="s">
         <v>1387</v>
@@ -17604,15 +17610,15 @@
     </row>
     <row r="1567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1567" t="s">
-        <v>1400</v>
+        <v>764</v>
       </c>
       <c r="B1567" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="1568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1568" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B1568" t="s">
         <v>1401</v>
@@ -17620,7 +17626,7 @@
     </row>
     <row r="1569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B1569" t="s">
         <v>1401</v>
@@ -17628,7 +17634,7 @@
     </row>
     <row r="1570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1570" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B1570" t="s">
         <v>1401</v>
@@ -17636,7 +17642,7 @@
     </row>
     <row r="1571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1571" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B1571" t="s">
         <v>1401</v>
@@ -17644,7 +17650,7 @@
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1572" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B1572" t="s">
         <v>1401</v>
@@ -17652,7 +17658,7 @@
     </row>
     <row r="1573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1573" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1573" t="s">
         <v>1401</v>
@@ -17660,7 +17666,7 @@
     </row>
     <row r="1574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1574" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1574" t="s">
         <v>1401</v>
@@ -17668,7 +17674,7 @@
     </row>
     <row r="1575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1575" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1575" t="s">
         <v>1401</v>
@@ -17676,7 +17682,7 @@
     </row>
     <row r="1576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B1576" t="s">
         <v>1401</v>
@@ -17684,7 +17690,7 @@
     </row>
     <row r="1577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B1577" t="s">
         <v>1401</v>
@@ -17692,15 +17698,15 @@
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1578" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B1578" t="s">
-        <v>1413</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="1579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1579" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B1579" t="s">
         <v>1413</v>
@@ -17708,7 +17714,7 @@
     </row>
     <row r="1580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1580" t="s">
-        <v>1202</v>
+        <v>1414</v>
       </c>
       <c r="B1580" t="s">
         <v>1413</v>
@@ -17716,7 +17722,7 @@
     </row>
     <row r="1581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1581" t="s">
-        <v>1415</v>
+        <v>1202</v>
       </c>
       <c r="B1581" t="s">
         <v>1413</v>
@@ -17724,7 +17730,7 @@
     </row>
     <row r="1582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1582" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B1582" t="s">
         <v>1413</v>
@@ -17732,7 +17738,7 @@
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1583" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B1583" t="s">
         <v>1413</v>
@@ -17740,7 +17746,7 @@
     </row>
     <row r="1584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B1584" t="s">
         <v>1413</v>
@@ -17748,7 +17754,7 @@
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1585" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B1585" t="s">
         <v>1413</v>
@@ -17756,7 +17762,7 @@
     </row>
     <row r="1586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1586" t="s">
-        <v>1056</v>
+        <v>1419</v>
       </c>
       <c r="B1586" t="s">
         <v>1413</v>
@@ -17764,7 +17770,7 @@
     </row>
     <row r="1587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1587" t="s">
-        <v>1420</v>
+        <v>1056</v>
       </c>
       <c r="B1587" t="s">
         <v>1413</v>
@@ -17772,7 +17778,7 @@
     </row>
     <row r="1588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1588" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B1588" t="s">
         <v>1413</v>
@@ -17780,7 +17786,7 @@
     </row>
     <row r="1589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
-        <v>1224</v>
+        <v>1421</v>
       </c>
       <c r="B1589" t="s">
         <v>1413</v>
@@ -17788,7 +17794,7 @@
     </row>
     <row r="1590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1590" t="s">
-        <v>534</v>
+        <v>1224</v>
       </c>
       <c r="B1590" t="s">
         <v>1413</v>
@@ -17796,7 +17802,7 @@
     </row>
     <row r="1591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1591" t="s">
-        <v>1422</v>
+        <v>534</v>
       </c>
       <c r="B1591" t="s">
         <v>1413</v>
@@ -17804,15 +17810,15 @@
     </row>
     <row r="1592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B1592" t="s">
-        <v>1424</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="1593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1593" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B1593" t="s">
         <v>1424</v>
@@ -17820,7 +17826,7 @@
     </row>
     <row r="1594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1594" t="s">
         <v>1424</v>
@@ -17828,7 +17834,7 @@
     </row>
     <row r="1595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1595" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1595" t="s">
         <v>1424</v>
@@ -17836,7 +17842,7 @@
     </row>
     <row r="1596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B1596" t="s">
         <v>1424</v>
@@ -17844,7 +17850,7 @@
     </row>
     <row r="1597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1597" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B1597" t="s">
         <v>1424</v>
@@ -17852,7 +17858,7 @@
     </row>
     <row r="1598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1598" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1598" t="s">
         <v>1424</v>
@@ -17860,7 +17866,7 @@
     </row>
     <row r="1599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1599" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1599" t="s">
         <v>1424</v>
@@ -17868,7 +17874,7 @@
     </row>
     <row r="1600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1600" t="s">
-        <v>1030</v>
+        <v>1431</v>
       </c>
       <c r="B1600" t="s">
         <v>1424</v>
@@ -17876,7 +17882,7 @@
     </row>
     <row r="1601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1601" t="s">
-        <v>1432</v>
+        <v>1030</v>
       </c>
       <c r="B1601" t="s">
         <v>1424</v>
@@ -17884,7 +17890,7 @@
     </row>
     <row r="1602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1602" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1602" t="s">
         <v>1424</v>
@@ -17892,7 +17898,7 @@
     </row>
     <row r="1603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1603" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1603" t="s">
         <v>1424</v>
@@ -17900,7 +17906,7 @@
     </row>
     <row r="1604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1604" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1604" t="s">
         <v>1424</v>
@@ -17908,7 +17914,7 @@
     </row>
     <row r="1605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1605" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1605" t="s">
         <v>1424</v>
@@ -17916,7 +17922,7 @@
     </row>
     <row r="1606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1606" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B1606" t="s">
         <v>1424</v>
@@ -17924,7 +17930,7 @@
     </row>
     <row r="1607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B1607" t="s">
         <v>1424</v>
@@ -17932,7 +17938,7 @@
     </row>
     <row r="1608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1608" t="s">
-        <v>327</v>
+        <v>1438</v>
       </c>
       <c r="B1608" t="s">
         <v>1424</v>
@@ -17940,7 +17946,7 @@
     </row>
     <row r="1609" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1609" t="s">
-        <v>707</v>
+        <v>327</v>
       </c>
       <c r="B1609" t="s">
         <v>1424</v>
@@ -17948,7 +17954,7 @@
     </row>
     <row r="1610" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1610" t="s">
-        <v>1439</v>
+        <v>707</v>
       </c>
       <c r="B1610" t="s">
         <v>1424</v>
@@ -17956,7 +17962,7 @@
     </row>
     <row r="1611" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1611" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B1611" t="s">
         <v>1424</v>
@@ -17964,7 +17970,7 @@
     </row>
     <row r="1612" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1612" t="s">
         <v>1424</v>
@@ -17972,7 +17978,7 @@
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1613" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1613" t="s">
         <v>1424</v>
@@ -17980,7 +17986,7 @@
     </row>
     <row r="1614" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1614" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1614" t="s">
         <v>1424</v>
@@ -17988,7 +17994,7 @@
     </row>
     <row r="1615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B1615" t="s">
         <v>1424</v>
@@ -17996,7 +18002,7 @@
     </row>
     <row r="1616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1616" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B1616" t="s">
         <v>1424</v>
@@ -18004,7 +18010,7 @@
     </row>
     <row r="1617" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B1617" t="s">
         <v>1424</v>
@@ -18012,7 +18018,7 @@
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1618" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1618" t="s">
         <v>1424</v>
@@ -18020,15 +18026,15 @@
     </row>
     <row r="1619" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1619" t="s">
-        <v>121</v>
+        <v>1447</v>
       </c>
       <c r="B1619" t="s">
-        <v>1448</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1620" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1620" t="s">
-        <v>1449</v>
+        <v>121</v>
       </c>
       <c r="B1620" t="s">
         <v>1448</v>
@@ -18036,7 +18042,7 @@
     </row>
     <row r="1621" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1621" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B1621" t="s">
         <v>1448</v>
@@ -18044,7 +18050,7 @@
     </row>
     <row r="1622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1622" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1622" t="s">
         <v>1448</v>
@@ -18052,7 +18058,7 @@
     </row>
     <row r="1623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1623" t="s">
         <v>1448</v>
@@ -18060,7 +18066,7 @@
     </row>
     <row r="1624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1624" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1624" t="s">
         <v>1448</v>
@@ -18068,7 +18074,7 @@
     </row>
     <row r="1625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1625" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1625" t="s">
         <v>1448</v>
@@ -18076,7 +18082,7 @@
     </row>
     <row r="1626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1626" t="s">
         <v>1448</v>
@@ -18084,7 +18090,7 @@
     </row>
     <row r="1627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1627" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1627" t="s">
         <v>1448</v>
@@ -18092,7 +18098,7 @@
     </row>
     <row r="1628" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1628" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1628" t="s">
         <v>1448</v>
@@ -18100,7 +18106,7 @@
     </row>
     <row r="1629" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1629" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1629" t="s">
         <v>1448</v>
@@ -18108,7 +18114,7 @@
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1630" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1630" t="s">
         <v>1448</v>
@@ -18116,7 +18122,7 @@
     </row>
     <row r="1631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1631" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1631" t="s">
         <v>1448</v>
@@ -18124,7 +18130,7 @@
     </row>
     <row r="1632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1632" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1632" t="s">
         <v>1448</v>
@@ -18132,7 +18138,7 @@
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1633" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1633" t="s">
         <v>1448</v>
@@ -18140,7 +18146,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1634" t="s">
         <v>1448</v>
@@ -18148,7 +18154,7 @@
     </row>
     <row r="1635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1635" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1635" t="s">
         <v>1448</v>
@@ -18156,7 +18162,7 @@
     </row>
     <row r="1636" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1636" t="s">
-        <v>1220</v>
+        <v>1464</v>
       </c>
       <c r="B1636" t="s">
         <v>1448</v>
@@ -18164,7 +18170,7 @@
     </row>
     <row r="1637" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1637" t="s">
-        <v>1465</v>
+        <v>1220</v>
       </c>
       <c r="B1637" t="s">
         <v>1448</v>
@@ -18172,7 +18178,7 @@
     </row>
     <row r="1638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1638" t="s">
-        <v>249</v>
+        <v>1465</v>
       </c>
       <c r="B1638" t="s">
         <v>1448</v>
@@ -18180,7 +18186,7 @@
     </row>
     <row r="1639" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
-        <v>713</v>
+        <v>249</v>
       </c>
       <c r="B1639" t="s">
         <v>1448</v>
@@ -18188,7 +18194,7 @@
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1640" t="s">
-        <v>1466</v>
+        <v>713</v>
       </c>
       <c r="B1640" t="s">
         <v>1448</v>
@@ -18196,7 +18202,7 @@
     </row>
     <row r="1641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1641" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B1641" t="s">
         <v>1448</v>
@@ -18204,7 +18210,7 @@
     </row>
     <row r="1642" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1642" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1642" t="s">
         <v>1448</v>
@@ -18212,7 +18218,7 @@
     </row>
     <row r="1643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1643" t="s">
         <v>1448</v>
@@ -18220,15 +18226,15 @@
     </row>
     <row r="1644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1644" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1644" t="s">
         <v>1448</v>
       </c>
     </row>
     <row r="1645" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1645" s="2" t="s">
-        <v>1471</v>
+      <c r="A1645" t="s">
+        <v>1470</v>
       </c>
       <c r="B1645" t="s">
         <v>1448</v>
@@ -18236,7 +18242,7 @@
     </row>
     <row r="1646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1646" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1646" t="s">
         <v>1448</v>
@@ -18244,15 +18250,15 @@
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1647" s="2" t="s">
-        <v>217</v>
+        <v>1472</v>
       </c>
       <c r="B1647" t="s">
-        <v>1473</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1648" s="2" t="s">
-        <v>1474</v>
+        <v>217</v>
       </c>
       <c r="B1648" t="s">
         <v>1473</v>
@@ -18260,7 +18266,7 @@
     </row>
     <row r="1649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1649" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1649" t="s">
         <v>1473</v>
@@ -18268,7 +18274,7 @@
     </row>
     <row r="1650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1650" s="2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1650" t="s">
         <v>1473</v>
@@ -18276,7 +18282,7 @@
     </row>
     <row r="1651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1651" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1651" t="s">
         <v>1473</v>
@@ -18284,7 +18290,7 @@
     </row>
     <row r="1652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1652" s="2" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1652" t="s">
         <v>1473</v>
@@ -18292,7 +18298,7 @@
     </row>
     <row r="1653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1653" s="2" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1653" t="s">
         <v>1473</v>
@@ -18300,7 +18306,7 @@
     </row>
     <row r="1654" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1654" s="2" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1654" t="s">
         <v>1473</v>
@@ -18308,7 +18314,7 @@
     </row>
     <row r="1655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1655" s="2" t="s">
-        <v>468</v>
+        <v>1480</v>
       </c>
       <c r="B1655" t="s">
         <v>1473</v>
@@ -18316,7 +18322,7 @@
     </row>
     <row r="1656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1656" s="2" t="s">
-        <v>1481</v>
+        <v>468</v>
       </c>
       <c r="B1656" t="s">
         <v>1473</v>
@@ -18324,7 +18330,7 @@
     </row>
     <row r="1657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1657" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1657" t="s">
         <v>1473</v>
@@ -18332,7 +18338,7 @@
     </row>
     <row r="1658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1658" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1658" t="s">
         <v>1473</v>
@@ -18340,7 +18346,7 @@
     </row>
     <row r="1659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1659" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1659" t="s">
         <v>1473</v>
@@ -18348,7 +18354,7 @@
     </row>
     <row r="1660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1660" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1660" t="s">
         <v>1473</v>
@@ -18356,17 +18362,25 @@
     </row>
     <row r="1661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1661" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B1661" t="s">
         <v>1473</v>
       </c>
     </row>
     <row r="1662" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1662" s="3" t="s">
+      <c r="A1662" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1663" s="3" t="s">
         <v>1487</v>
       </c>
-      <c r="B1662" t="s">
+      <c r="B1663" t="s">
         <v>1473</v>
       </c>
     </row>
